--- a/รายชื่อและสารอาหาร.xlsx
+++ b/รายชื่อและสารอาหาร.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\dw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050944EB-A586-484B-9EC0-54204D4AD4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B99E91-1F16-46D0-BD02-13CDE27C7770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1275" yWindow="3270" windowWidth="21600" windowHeight="11295" xr2:uid="{4C22F895-6925-4FAB-963D-F8A1785B734D}"/>
+    <workbookView xWindow="9825" yWindow="2805" windowWidth="21600" windowHeight="11295" xr2:uid="{4C22F895-6925-4FAB-963D-F8A1785B734D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -971,9 +971,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -985,6 +982,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1324,11 +1324,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
       <c r="D1" s="3" t="s">
         <v>206</v>
       </c>
@@ -4088,19 +4088,19 @@
       <c r="C109" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="D109" s="26">
+      <c r="D109" s="25">
         <v>24.26</v>
       </c>
-      <c r="E109" s="26">
+      <c r="E109" s="25">
         <v>335</v>
       </c>
       <c r="F109" s="14">
         <v>4.5599999999999996</v>
       </c>
-      <c r="G109" s="26">
+      <c r="G109" s="25">
         <v>4.1399999999999997</v>
       </c>
-      <c r="H109" s="27">
+      <c r="H109" s="26">
         <v>160</v>
       </c>
     </row>
@@ -4114,19 +4114,19 @@
       <c r="C110" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="D110" s="26">
+      <c r="D110" s="25">
         <v>2.86</v>
       </c>
-      <c r="E110" s="26">
+      <c r="E110" s="25">
         <v>521</v>
       </c>
       <c r="F110" s="14">
         <v>4.67</v>
       </c>
-      <c r="G110" s="26">
+      <c r="G110" s="25">
         <v>1.43</v>
       </c>
-      <c r="H110" s="27">
+      <c r="H110" s="26">
         <v>44</v>
       </c>
     </row>
@@ -4140,19 +4140,19 @@
       <c r="C111" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="D111" s="26">
+      <c r="D111" s="25">
         <v>2.4</v>
       </c>
-      <c r="E111" s="26">
+      <c r="E111" s="25">
         <v>350</v>
       </c>
       <c r="F111" s="14">
         <v>18.2</v>
       </c>
-      <c r="G111" s="26">
+      <c r="G111" s="25">
         <v>19.5</v>
       </c>
-      <c r="H111" s="27">
+      <c r="H111" s="26">
         <v>265</v>
       </c>
     </row>
@@ -4166,16 +4166,16 @@
       <c r="C112" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="D112" s="26">
+      <c r="D112" s="25">
         <v>1</v>
       </c>
-      <c r="E112" s="26">
+      <c r="E112" s="25">
         <v>450</v>
       </c>
-      <c r="F112" s="26">
+      <c r="F112" s="25">
         <v>18</v>
       </c>
-      <c r="G112" s="26">
+      <c r="G112" s="25">
         <v>1.5</v>
       </c>
       <c r="H112" s="14">
@@ -4192,16 +4192,16 @@
       <c r="C113" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="D113" s="26">
+      <c r="D113" s="25">
         <v>8.5</v>
       </c>
-      <c r="E113" s="26">
+      <c r="E113" s="25">
         <v>700</v>
       </c>
-      <c r="F113" s="26">
+      <c r="F113" s="25">
         <v>9</v>
       </c>
-      <c r="G113" s="26">
+      <c r="G113" s="25">
         <v>10</v>
       </c>
       <c r="H113" s="14">
@@ -4218,16 +4218,16 @@
       <c r="C114" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="D114" s="26">
+      <c r="D114" s="25">
         <v>34</v>
       </c>
-      <c r="E114" s="26">
+      <c r="E114" s="25">
         <v>120</v>
       </c>
-      <c r="F114" s="26">
+      <c r="F114" s="25">
         <v>2.5</v>
       </c>
-      <c r="G114" s="26">
+      <c r="G114" s="25">
         <v>6.5</v>
       </c>
       <c r="H114" s="14">
@@ -4244,28 +4244,28 @@
       <c r="C115" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="D115" s="26">
+      <c r="D115" s="25">
         <v>12.65</v>
       </c>
-      <c r="E115" s="26">
+      <c r="E115" s="25">
         <v>313</v>
       </c>
-      <c r="F115" s="26">
+      <c r="F115" s="25">
         <v>10.28</v>
       </c>
-      <c r="G115" s="26">
+      <c r="G115" s="25">
         <v>10.99</v>
       </c>
-      <c r="H115" s="28">
+      <c r="H115" s="27">
         <v>194</v>
       </c>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="25"/>
+      <c r="A116" s="24"/>
       <c r="H116" s="1"/>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" s="25"/>
+      <c r="A117" s="24"/>
       <c r="H117" s="2"/>
     </row>
     <row r="118" spans="1:8">
